--- a/SSIM_Table.xlsx
+++ b/SSIM_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esray\Desktop\comparison_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC04C675-40ED-4D1D-9086-0CD9364AAD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0C4125D-C2FF-4F04-B938-B3ECB8911F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B95ED7DB-A3ED-40C0-A5F5-336F6AAF9896}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CA3FD7-475E-4FC8-B5EA-E1845871D73D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -445,7 +448,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{372B78A0-6D06-4C8A-94E2-A703B32C9C34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C591149-CCB5-43CD-8A8F-E1E515F8A383}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -599,7 +602,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6FB3878-5695-40A0-89B8-F7223359772F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7019053-5182-4A78-B803-8C5DE9898BAD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -608,7 +611,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{849ED6D9-ECCD-423C-B70C-C96442BB7F1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92A14FFC-5AB0-45B5-9455-87277EBB0E2B}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
